--- a/assets/标准地址表模板.xlsx
+++ b/assets/标准地址表模板.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21652" windowHeight="11415" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标准地址" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="标准地址" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -188,6 +188,11 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Noto Serif SC"/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
     </font>
   </fonts>
   <fills count="34">
@@ -674,7 +679,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -687,6 +692,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyFont="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1100,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1315,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>&lt;分纤箱编号&gt;</t>
+          <t>&lt;分纤箱编号（安装楼层）&gt;</t>
         </is>
       </c>
       <c r="Q2" s="2" t="n"/>
@@ -1331,6 +1339,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>AI生成 | 生成内容标识 | 2026-09-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
